--- a/docs/ATLAS_REVIEW_CONFIRMATION.xlsx
+++ b/docs/ATLAS_REVIEW_CONFIRMATION.xlsx
@@ -71,7 +71,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -103,6 +103,11 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -130,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -156,11 +161,14 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -652,7 +660,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Accepted / Yes / Pass</t>
+          <t>Accept recommendation / Accept / Yes / N/A / Pass</t>
         </is>
       </c>
     </row>
@@ -730,8 +738,9 @@
           <t>1 Decisions</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n">
-        <v>14</v>
+      <c r="B21" s="12">
+        <f>COUNTA('1 Decisions'!$A$5:$A$18)</f>
+        <v/>
       </c>
       <c r="C21" s="12">
         <f>B21-G21</f>
@@ -750,7 +759,7 @@
         <v/>
       </c>
       <c r="G21" s="12">
-        <f>COUNTBLANK('1 Decisions'!$E$5:$E$18)+COUNTIF('1 Decisions'!$E$5:$E$18,"Not yet run")</f>
+        <f>COUNTBLANK('1 Decisions'!$E$5:$E$18)</f>
         <v/>
       </c>
     </row>
@@ -760,8 +769,9 @@
           <t>2 Resolutions</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n">
-        <v>20</v>
+      <c r="B22" s="12">
+        <f>COUNTA('2 Resolutions'!$A$5:$A$24)</f>
+        <v/>
       </c>
       <c r="C22" s="12">
         <f>B22-G22</f>
@@ -780,7 +790,7 @@
         <v/>
       </c>
       <c r="G22" s="12">
-        <f>COUNTBLANK('2 Resolutions'!$D$5:$D$24)+COUNTIF('2 Resolutions'!$D$5:$D$24,"Not yet run")</f>
+        <f>COUNTBLANK('2 Resolutions'!$D$5:$D$24)</f>
         <v/>
       </c>
     </row>
@@ -790,8 +800,9 @@
           <t>3 Risks</t>
         </is>
       </c>
-      <c r="B23" s="12" t="n">
-        <v>18</v>
+      <c r="B23" s="12">
+        <f>COUNTA('3 Risks'!$A$5:$A$22)</f>
+        <v/>
       </c>
       <c r="C23" s="12">
         <f>B23-G23</f>
@@ -810,7 +821,7 @@
         <v/>
       </c>
       <c r="G23" s="12">
-        <f>COUNTBLANK('3 Risks'!$F$5:$F$22)+COUNTIF('3 Risks'!$F$5:$F$22,"Not yet run")</f>
+        <f>COUNTBLANK('3 Risks'!$F$5:$F$22)</f>
         <v/>
       </c>
     </row>
@@ -820,8 +831,9 @@
           <t>4 Verification</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n">
-        <v>18</v>
+      <c r="B24" s="12">
+        <f>COUNTA('4 Verification'!$A$5:$A$22)</f>
+        <v/>
       </c>
       <c r="C24" s="12">
         <f>B24-G24</f>
@@ -850,8 +862,9 @@
           <t>5 Checklist</t>
         </is>
       </c>
-      <c r="B25" s="12" t="n">
-        <v>14</v>
+      <c r="B25" s="12">
+        <f>COUNTA('5 Checklist'!$A$5:$A$18)</f>
+        <v/>
       </c>
       <c r="C25" s="12">
         <f>B25-G25</f>
@@ -870,7 +883,7 @@
         <v/>
       </c>
       <c r="G25" s="12">
-        <f>COUNTBLANK('5 Checklist'!$D$5:$D$18)+COUNTIF('5 Checklist'!$D$5:$D$18,"Not yet run")</f>
+        <f>COUNTBLANK('5 Checklist'!$D$5:$D$18)</f>
         <v/>
       </c>
     </row>
@@ -915,7 +928,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Example of a completed decision row (format only; not a real answer)</t>
+          <t>Example of a completed decision row (format only, not editable, not counted; grey marks where your text would go)</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1672,6 +1685,13 @@
       <c r="D26" s="11" t="inlineStr">
         <is>
           <t>Kokoro preset</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Known conflict: Arthur, Victor, and Gideon all pull toward the same four British male presets. Once heard, expect to spread them apart or move one to a Chatterbox clone, as Alaric is.</t>
         </is>
       </c>
     </row>
@@ -3315,8 +3335,8 @@
         </is>
       </c>
       <c r="E5" s="16" t="n"/>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="F5" s="17" t="n"/>
+      <c r="G5" s="17" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -3340,8 +3360,8 @@
         </is>
       </c>
       <c r="E6" s="16" t="n"/>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="17" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -3365,8 +3385,8 @@
         </is>
       </c>
       <c r="E7" s="16" t="n"/>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -3390,8 +3410,8 @@
         </is>
       </c>
       <c r="E8" s="16" t="n"/>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="17" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -3415,8 +3435,8 @@
         </is>
       </c>
       <c r="E9" s="16" t="n"/>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="17" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -3440,8 +3460,8 @@
         </is>
       </c>
       <c r="E10" s="16" t="n"/>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="17" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -3465,8 +3485,8 @@
         </is>
       </c>
       <c r="E11" s="16" t="n"/>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="F11" s="17" t="n"/>
+      <c r="G11" s="17" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -3490,8 +3510,8 @@
         </is>
       </c>
       <c r="E12" s="16" t="n"/>
-      <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="17" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -3515,8 +3535,8 @@
         </is>
       </c>
       <c r="E13" s="16" t="n"/>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="17" t="n"/>
+      <c r="G13" s="17" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -3540,8 +3560,8 @@
         </is>
       </c>
       <c r="E14" s="16" t="n"/>
-      <c r="F14" s="15" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="F14" s="17" t="n"/>
+      <c r="G14" s="17" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -3565,8 +3585,8 @@
         </is>
       </c>
       <c r="E15" s="16" t="n"/>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="17" t="n"/>
+      <c r="G15" s="17" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -3590,8 +3610,8 @@
         </is>
       </c>
       <c r="E16" s="16" t="n"/>
-      <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="F16" s="17" t="n"/>
+      <c r="G16" s="17" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -3615,8 +3635,8 @@
         </is>
       </c>
       <c r="E17" s="16" t="n"/>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="F17" s="17" t="n"/>
+      <c r="G17" s="17" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -3640,8 +3660,8 @@
         </is>
       </c>
       <c r="E18" s="16" t="n"/>
-      <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="F18" s="17" t="n"/>
+      <c r="G18" s="17" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:G18"/>
@@ -3657,7 +3677,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E5:E18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." promptTitle="Choose" prompt="Pick one: Accept recommendation / Change / Need more information" type="list">
+    <dataValidation sqref="E5:E18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." promptTitle="Choose" prompt="Pick one: Accept recommendation / Change / Need more information" type="list" errorStyle="stop">
       <formula1>"Accept recommendation,Change,Need more information"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3739,7 +3759,7 @@
         </is>
       </c>
       <c r="D5" s="16" t="n"/>
-      <c r="E5" s="15" t="n"/>
+      <c r="E5" s="17" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -3758,7 +3778,7 @@
         </is>
       </c>
       <c r="D6" s="16" t="n"/>
-      <c r="E6" s="15" t="n"/>
+      <c r="E6" s="17" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -3777,7 +3797,7 @@
         </is>
       </c>
       <c r="D7" s="16" t="n"/>
-      <c r="E7" s="15" t="n"/>
+      <c r="E7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -3796,7 +3816,7 @@
         </is>
       </c>
       <c r="D8" s="16" t="n"/>
-      <c r="E8" s="15" t="n"/>
+      <c r="E8" s="17" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -3815,7 +3835,7 @@
         </is>
       </c>
       <c r="D9" s="16" t="n"/>
-      <c r="E9" s="15" t="n"/>
+      <c r="E9" s="17" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -3834,7 +3854,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n"/>
-      <c r="E10" s="15" t="n"/>
+      <c r="E10" s="17" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -3853,7 +3873,7 @@
         </is>
       </c>
       <c r="D11" s="16" t="n"/>
-      <c r="E11" s="15" t="n"/>
+      <c r="E11" s="17" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -3872,7 +3892,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n"/>
-      <c r="E12" s="15" t="n"/>
+      <c r="E12" s="17" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -3891,7 +3911,7 @@
         </is>
       </c>
       <c r="D13" s="16" t="n"/>
-      <c r="E13" s="15" t="n"/>
+      <c r="E13" s="17" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -3910,7 +3930,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n"/>
-      <c r="E14" s="15" t="n"/>
+      <c r="E14" s="17" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -3929,7 +3949,7 @@
         </is>
       </c>
       <c r="D15" s="16" t="n"/>
-      <c r="E15" s="15" t="n"/>
+      <c r="E15" s="17" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -3948,7 +3968,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n"/>
-      <c r="E16" s="15" t="n"/>
+      <c r="E16" s="17" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -3967,7 +3987,7 @@
         </is>
       </c>
       <c r="D17" s="16" t="n"/>
-      <c r="E17" s="15" t="n"/>
+      <c r="E17" s="17" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -3986,7 +4006,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n"/>
-      <c r="E18" s="15" t="n"/>
+      <c r="E18" s="17" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -4005,7 +4025,7 @@
         </is>
       </c>
       <c r="D19" s="16" t="n"/>
-      <c r="E19" s="15" t="n"/>
+      <c r="E19" s="17" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -4024,7 +4044,7 @@
         </is>
       </c>
       <c r="D20" s="16" t="n"/>
-      <c r="E20" s="15" t="n"/>
+      <c r="E20" s="17" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -4043,7 +4063,7 @@
         </is>
       </c>
       <c r="D21" s="16" t="n"/>
-      <c r="E21" s="15" t="n"/>
+      <c r="E21" s="17" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -4062,7 +4082,7 @@
         </is>
       </c>
       <c r="D22" s="16" t="n"/>
-      <c r="E22" s="15" t="n"/>
+      <c r="E22" s="17" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -4081,7 +4101,7 @@
         </is>
       </c>
       <c r="D23" s="16" t="n"/>
-      <c r="E23" s="15" t="n"/>
+      <c r="E23" s="17" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -4100,7 +4120,7 @@
         </is>
       </c>
       <c r="D24" s="16" t="n"/>
-      <c r="E24" s="15" t="n"/>
+      <c r="E24" s="17" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:E24"/>
@@ -4113,7 +4133,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D5:D24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." promptTitle="Choose" prompt="Pick one: Accept / Disagree - return to decisions" type="list">
+    <dataValidation sqref="D5:D24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." promptTitle="Choose" prompt="Pick one: Accept / Disagree - return to decisions" type="list" errorStyle="stop">
       <formula1>"Accept,Disagree - return to decisions"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4217,7 +4237,7 @@
         </is>
       </c>
       <c r="F5" s="16" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="G5" s="17" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -4246,7 +4266,7 @@
         </is>
       </c>
       <c r="F6" s="16" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="G6" s="17" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -4275,7 +4295,7 @@
         </is>
       </c>
       <c r="F7" s="16" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="G7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -4304,7 +4324,7 @@
         </is>
       </c>
       <c r="F8" s="16" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="G8" s="17" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -4333,7 +4353,7 @@
         </is>
       </c>
       <c r="F9" s="16" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="G9" s="17" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -4362,7 +4382,7 @@
         </is>
       </c>
       <c r="F10" s="16" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="G10" s="17" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -4391,7 +4411,7 @@
         </is>
       </c>
       <c r="F11" s="16" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="G11" s="17" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -4420,7 +4440,7 @@
         </is>
       </c>
       <c r="F12" s="16" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="G12" s="17" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -4449,7 +4469,7 @@
         </is>
       </c>
       <c r="F13" s="16" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="G13" s="17" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -4478,7 +4498,7 @@
         </is>
       </c>
       <c r="F14" s="16" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="G14" s="17" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -4507,7 +4527,7 @@
         </is>
       </c>
       <c r="F15" s="16" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="G15" s="17" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -4536,7 +4556,7 @@
         </is>
       </c>
       <c r="F16" s="16" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="G16" s="17" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -4565,7 +4585,7 @@
         </is>
       </c>
       <c r="F17" s="16" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="G17" s="17" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -4594,7 +4614,7 @@
         </is>
       </c>
       <c r="F18" s="16" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="G18" s="17" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -4623,7 +4643,7 @@
         </is>
       </c>
       <c r="F19" s="16" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="G19" s="17" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -4652,7 +4672,7 @@
         </is>
       </c>
       <c r="F20" s="16" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="G20" s="17" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -4681,7 +4701,7 @@
         </is>
       </c>
       <c r="F21" s="16" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="G21" s="17" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -4710,7 +4730,7 @@
         </is>
       </c>
       <c r="F22" s="16" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="G22" s="17" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:G22"/>
@@ -4718,12 +4738,12 @@
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="2">
       <formula>"Discuss"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." promptTitle="Choose" prompt="Pick one: Yes / Discuss" type="list">
+    <dataValidation sqref="F5:F22" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." promptTitle="Choose" prompt="Pick one: Yes / Discuss" type="list" errorStyle="stop">
       <formula1>"Yes,Discuss"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4809,7 +4829,7 @@
           <t>Not yet run</t>
         </is>
       </c>
-      <c r="E5" s="15" t="n"/>
+      <c r="E5" s="17" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -4832,7 +4852,7 @@
           <t>Not yet run</t>
         </is>
       </c>
-      <c r="E6" s="15" t="n"/>
+      <c r="E6" s="17" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -4855,7 +4875,7 @@
           <t>Not yet run</t>
         </is>
       </c>
-      <c r="E7" s="15" t="n"/>
+      <c r="E7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -4878,7 +4898,7 @@
           <t>Not yet run</t>
         </is>
       </c>
-      <c r="E8" s="15" t="n"/>
+      <c r="E8" s="17" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -4901,7 +4921,7 @@
           <t>Not yet run</t>
         </is>
       </c>
-      <c r="E9" s="15" t="n"/>
+      <c r="E9" s="17" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -4924,7 +4944,7 @@
           <t>Not yet run</t>
         </is>
       </c>
-      <c r="E10" s="15" t="n"/>
+      <c r="E10" s="17" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -4947,7 +4967,7 @@
           <t>Not yet run</t>
         </is>
       </c>
-      <c r="E11" s="15" t="n"/>
+      <c r="E11" s="17" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -4970,7 +4990,7 @@
           <t>Not yet run</t>
         </is>
       </c>
-      <c r="E12" s="15" t="n"/>
+      <c r="E12" s="17" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -4993,7 +5013,7 @@
           <t>Not yet run</t>
         </is>
       </c>
-      <c r="E13" s="15" t="n"/>
+      <c r="E13" s="17" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -5016,7 +5036,7 @@
           <t>Not yet run</t>
         </is>
       </c>
-      <c r="E14" s="15" t="n"/>
+      <c r="E14" s="17" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -5039,7 +5059,7 @@
           <t>Not yet run</t>
         </is>
       </c>
-      <c r="E15" s="15" t="n"/>
+      <c r="E15" s="17" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -5062,7 +5082,7 @@
           <t>Not yet run</t>
         </is>
       </c>
-      <c r="E16" s="15" t="n"/>
+      <c r="E16" s="17" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -5085,7 +5105,7 @@
           <t>Not yet run</t>
         </is>
       </c>
-      <c r="E17" s="15" t="n"/>
+      <c r="E17" s="17" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -5108,7 +5128,7 @@
           <t>Not yet run</t>
         </is>
       </c>
-      <c r="E18" s="15" t="n"/>
+      <c r="E18" s="17" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -5131,7 +5151,7 @@
           <t>Not yet run</t>
         </is>
       </c>
-      <c r="E19" s="15" t="n"/>
+      <c r="E19" s="17" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -5154,7 +5174,7 @@
           <t>Not yet run</t>
         </is>
       </c>
-      <c r="E20" s="15" t="n"/>
+      <c r="E20" s="17" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -5177,7 +5197,7 @@
           <t>Not yet run</t>
         </is>
       </c>
-      <c r="E21" s="15" t="n"/>
+      <c r="E21" s="17" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -5200,7 +5220,7 @@
           <t>Not yet run</t>
         </is>
       </c>
-      <c r="E22" s="15" t="n"/>
+      <c r="E22" s="17" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:E22"/>
@@ -5219,7 +5239,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D5:D22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." promptTitle="Choose" prompt="Pick one: Pass / Fail / Deferred / Not yet run" type="list">
+    <dataValidation sqref="D5:D22" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." promptTitle="Choose" prompt="Pick one: Pass / Fail / Deferred / Not yet run" type="list" errorStyle="stop">
       <formula1>"Pass,Fail,Deferred,Not yet run"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5236,7 +5256,7 @@
   <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -5299,7 +5319,7 @@
         </is>
       </c>
       <c r="D5" s="16" t="n"/>
-      <c r="E5" s="15" t="n"/>
+      <c r="E5" s="17" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="n">
@@ -5316,7 +5336,7 @@
         </is>
       </c>
       <c r="D6" s="16" t="n"/>
-      <c r="E6" s="15" t="n"/>
+      <c r="E6" s="17" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
@@ -5333,7 +5353,7 @@
         </is>
       </c>
       <c r="D7" s="16" t="n"/>
-      <c r="E7" s="15" t="n"/>
+      <c r="E7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="n">
@@ -5350,7 +5370,7 @@
         </is>
       </c>
       <c r="D8" s="16" t="n"/>
-      <c r="E8" s="15" t="n"/>
+      <c r="E8" s="17" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
@@ -5367,7 +5387,7 @@
         </is>
       </c>
       <c r="D9" s="16" t="n"/>
-      <c r="E9" s="15" t="n"/>
+      <c r="E9" s="17" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="n">
@@ -5384,7 +5404,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n"/>
-      <c r="E10" s="15" t="n"/>
+      <c r="E10" s="17" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
@@ -5401,7 +5421,7 @@
         </is>
       </c>
       <c r="D11" s="16" t="n"/>
-      <c r="E11" s="15" t="n"/>
+      <c r="E11" s="17" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="n">
@@ -5418,7 +5438,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n"/>
-      <c r="E12" s="15" t="n"/>
+      <c r="E12" s="17" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
@@ -5435,7 +5455,7 @@
         </is>
       </c>
       <c r="D13" s="16" t="n"/>
-      <c r="E13" s="15" t="n"/>
+      <c r="E13" s="17" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="n">
@@ -5452,7 +5472,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n"/>
-      <c r="E14" s="15" t="n"/>
+      <c r="E14" s="17" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
@@ -5469,7 +5489,7 @@
         </is>
       </c>
       <c r="D15" s="16" t="n"/>
-      <c r="E15" s="15" t="n"/>
+      <c r="E15" s="17" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="n">
@@ -5486,7 +5506,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n"/>
-      <c r="E16" s="15" t="n"/>
+      <c r="E16" s="17" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
@@ -5503,7 +5523,7 @@
         </is>
       </c>
       <c r="D17" s="16" t="n"/>
-      <c r="E17" s="15" t="n"/>
+      <c r="E17" s="17" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="n">
@@ -5520,7 +5540,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n"/>
-      <c r="E18" s="15" t="n"/>
+      <c r="E18" s="17" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:E18"/>
@@ -5536,7 +5556,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D5:D18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." promptTitle="Choose" prompt="Pick one: Yes / No / N/A" type="list">
+    <dataValidation sqref="D5:D18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." promptTitle="Choose" prompt="Pick one: Yes / No / N/A" type="list" errorStyle="stop">
       <formula1>"Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5550,7 +5570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5717,237 +5737,216 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Optional fifth (D12): Meditron-70B, dense, ~40 GB at 4-bit, single-digit tok/s, Minerva cross-check only, runs through llama.cpp in Phase 3 (C5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>The two hemispheres</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr"/>
-      <c r="B12" s="10" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Ren Ackerman — Vanguard, Prime Director</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>Arthur Sterling — Architect, Estate Manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Hemisphere</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>Offensive, creative, expansive, outward-facing</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Defensive, regimented, private, guardian of personal data</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Domain mandate</t>
+          <t>Hemisphere</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Corporate, Enterprise, Infrastructure, AEC</t>
+          <t>Offensive, creative, expansive, outward-facing</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Estate, Private Health, Logistics, Family</t>
+          <t>Defensive, regimented, private, guardian of personal data</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>Default engine</t>
+          <t>Domain mandate</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>gpt-oss-120b</t>
+          <t>Corporate, Enterprise, Infrastructure, AEC</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Nemotron 3 Super</t>
+          <t>Estate, Private Health, Logistics, Family</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>Override engine</t>
+          <t>Default engine</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>gpt-oss-120b abliterated, on Principal's order</t>
+          <t>gpt-oss-120b</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Qwen3.5-122B-A10B for deep document reasoning</t>
+          <t>Nemotron 3 Super</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Sampling</t>
+          <t>Override engine</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>High temperature (0.8) as Deep Think Generator</t>
+          <t>gpt-oss-120b abliterated, on Principal's order</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Low temperature, not zero, as Deep Think Adversary</t>
+          <t>Qwen3.5-122B-A10B for deep document reasoning</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Deep Think role</t>
+          <t>Sampling</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Generator: three divergent trajectories</t>
+          <t>High temperature (0.8) as Deep Think Generator</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Adversary: rubric-scored verdict, weak concepts killed</t>
+          <t>Low temperature, not zero, as Deep Think Adversary</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Code path</t>
+          <t>Deep Think role</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Writes sandbox code</t>
+          <t>Generator: three divergent trajectories</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Audits code for memory and safety before execution, as a second layer over the OS-level sandbox cap</t>
+          <t>Adversary: rubric-scored verdict, weak concepts killed</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
+          <t>Code path</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Writes sandbox code</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Audits code for memory and safety before execution, as a second layer over the OS-level sandbox cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
           <t>Directors</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Gideon, Silas, Valerie, Helena, Eleanor</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>Alaric, Minerva, Victor</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Shadow Cabinet engine map</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>Division</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>Remit</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>Default engine</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>Override</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>Speaks externally</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>Gideon Vance</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>Corporate</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>Legal &amp; Compliance</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>gpt-oss-120b, high reasoning, retrieval-grounded</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>Qwen3.5-122B for long contracts</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>Yes, sensitive tier</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Silas Thorne</t>
+          <t>Gideon Vance</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
@@ -5957,29 +5956,29 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>CFO: capital, audit, banking</t>
+          <t>Legal &amp; Compliance</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Nemotron 3 Super + code interpreter for all arithmetic</t>
+          <t>gpt-oss-120b, high reasoning, retrieval-grounded</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Qwen3.5-122B for long contracts</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>Yes, standard tier</t>
+          <t>Yes, sensitive tier</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>Valerie Cross</t>
+          <t>Silas Thorne</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
@@ -5989,17 +5988,17 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Infrastructure, DevOps, AEC, cyber, AEGIS Sandbox</t>
+          <t>CFO: capital, audit, banking</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>gpt-oss-120b abliterated</t>
+          <t>Nemotron 3 Super + code interpreter for all arithmetic</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Qwen3.5-122B for drawings and images</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -6011,7 +6010,7 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Helena Frost</t>
+          <t>Valerie Cross</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
@@ -6021,17 +6020,17 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Communications, brand, PR, crisis</t>
+          <t>Infrastructure, DevOps, AEC, cyber, AEGIS Sandbox</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>gpt-oss-120b</t>
+          <t>gpt-oss-120b abliterated</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Qwen3.5-122B for drawings and images</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -6043,7 +6042,7 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>Eleanor Croft</t>
+          <t>Helena Frost</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
@@ -6053,12 +6052,12 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Routing, scheduling, triage; the 4-Way Router's classifier</t>
+          <t>Communications, brand, PR, crisis</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Resident 4B model</t>
+          <t>gpt-oss-120b</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
@@ -6068,29 +6067,29 @@
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>Yes, routine tier (scheduling)</t>
+          <t>Yes, standard tier</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>Alaric Stone</t>
+          <t>Eleanor Croft</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Estate</t>
+          <t>Corporate</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Physical assets, security, threat mitigation; Sentinel threat watch</t>
+          <t>Routing, scheduling, triage; the 4-Way Router's classifier</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Nemotron 3 Super</t>
+          <t>Resident 4B model</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
@@ -6100,14 +6099,14 @@
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>Yes, sensitive tier</t>
+          <t>Yes, routine tier (scheduling)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>Minerva Hale</t>
+          <t>Alaric Stone</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
@@ -6117,17 +6116,17 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Private health, longevity; medical data</t>
+          <t>Physical assets, security, threat mitigation; Sentinel threat watch</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>gpt-oss-120b, retrieval-grounded</t>
+          <t>Nemotron 3 Super</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Qwen3.5-122B for records and scans; Meditron-70B cross-check</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -6139,30 +6138,62 @@
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
+          <t>Minerva Hale</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Estate</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Private health, longevity; medical data</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>gpt-oss-120b, retrieval-grounded</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Qwen3.5-122B for records and scans; Meditron-70B cross-check</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>Yes, sensitive tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
           <t>Victor Vale</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>Estate</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>Aviation, transport, concierge</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>gpt-oss-120b</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>Yes, routine tier</t>
         </is>

--- a/docs/ATLAS_REVIEW_CONFIRMATION.xlsx
+++ b/docs/ATLAS_REVIEW_CONFIRMATION.xlsx
@@ -615,7 +615,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>4. Sheet 4 (Verification) is filled during Day 1 as each phase gate runs, not now.</t>
+          <t>4. Sheet 4 (Verification) is filled during Day 1 as each phase gate runs, not now; its Result column shows amber 'Not yet run' until then.</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Need more information / Deferred / Not yet run</t>
+          <t>Need more information / Deferred / Not yet run (Not yet run counts as Remaining, not Hold)</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Change / Disagree / Discuss / No / Fail</t>
+          <t>Change / Disagree - return to decisions / Discuss / No / Fail</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Positive / Hold / Negative map to each sheet's dropdown: Decisions = Accept / Need more information / Change; Resolutions = Accept / - / Disagree; Risks = Yes / - / Discuss; Verification = Pass / Deferred / Fail; Checklist = Yes or N/A / - / No.</t>
+          <t>Positive / Hold / Negative map to each sheet's dropdown: Decisions = Accept / Need more information / Change; Resolutions = Accept / - / Disagree - return to decisions; Risks = Yes / - / Discuss; Verification = Pass / Deferred / Fail, with Not yet run counted as Remaining; Checklist = Yes or N/A / - / No.</t>
         </is>
       </c>
     </row>
